--- a/research/traditional_assets/database/data/south_korea/south_korea_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0199</v>
+        <v>0.0259</v>
       </c>
       <c r="E2">
-        <v>0.409</v>
+        <v>0.293</v>
       </c>
       <c r="G2">
-        <v>0.1628721541155867</v>
+        <v>0.102987777274785</v>
       </c>
       <c r="H2">
-        <v>0.1628721541155867</v>
+        <v>0.102987777274785</v>
       </c>
       <c r="I2">
-        <v>0.04010507880910683</v>
+        <v>0.04959257582616568</v>
       </c>
       <c r="J2">
-        <v>0.03176744400405568</v>
+        <v>0.03849413871225874</v>
       </c>
       <c r="K2">
-        <v>15.9</v>
+        <v>44.8</v>
       </c>
       <c r="L2">
-        <v>0.06961471103327496</v>
+        <v>0.101403349932096</v>
       </c>
       <c r="M2">
-        <v>6.6896</v>
+        <v>2.3504</v>
       </c>
       <c r="N2">
-        <v>0.03979535990481856</v>
+        <v>0.01662234794908063</v>
       </c>
       <c r="O2">
-        <v>0.4207295597484277</v>
+        <v>0.05246428571428572</v>
       </c>
       <c r="P2">
-        <v>6.6896</v>
+        <v>2.3504</v>
       </c>
       <c r="Q2">
-        <v>0.03979535990481856</v>
+        <v>0.01662234794908063</v>
       </c>
       <c r="R2">
-        <v>0.4207295597484277</v>
+        <v>0.05246428571428572</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>22.8</v>
+        <v>35.61</v>
       </c>
       <c r="V2">
-        <v>0.1356335514574658</v>
-      </c>
-      <c r="W2">
-        <v>0.232796486090776</v>
+        <v>0.2518387553041019</v>
       </c>
       <c r="X2">
-        <v>0.05332407744886498</v>
-      </c>
-      <c r="Y2">
-        <v>0.179472408641911</v>
+        <v>0.09247136790289856</v>
       </c>
       <c r="Z2">
-        <v>2.799877413423231</v>
-      </c>
-      <c r="AA2">
-        <v>0.08894494894914272</v>
+        <v>4.371227861877907</v>
       </c>
       <c r="AB2">
-        <v>0.04798775604345278</v>
-      </c>
-      <c r="AC2">
-        <v>0.04095719290568994</v>
+        <v>0.07925717318373224</v>
       </c>
       <c r="AD2">
-        <v>41.6</v>
+        <v>57.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>41.6</v>
+        <v>57.6</v>
       </c>
       <c r="AG2">
-        <v>18.8</v>
+        <v>21.99</v>
       </c>
       <c r="AH2">
-        <v>0.1983786361468765</v>
+        <v>0.2894472361809046</v>
       </c>
       <c r="AI2">
-        <v>0.2788203753351207</v>
+        <v>0.2456289978678038</v>
       </c>
       <c r="AJ2">
-        <v>0.1005885500267523</v>
+        <v>0.1345859599730706</v>
       </c>
       <c r="AK2">
-        <v>0.1487341772151899</v>
+        <v>0.1105636281361557</v>
       </c>
       <c r="AL2">
-        <v>1.08</v>
+        <v>1.971</v>
       </c>
       <c r="AM2">
-        <v>0.3490000000000001</v>
+        <v>-0.242</v>
       </c>
       <c r="AN2">
-        <v>1.69795918367347</v>
+        <v>1.355294117647059</v>
       </c>
       <c r="AO2">
-        <v>8.481481481481481</v>
+        <v>11.11618467782851</v>
       </c>
       <c r="AP2">
-        <v>0.7673469387755102</v>
+        <v>0.5174117647058823</v>
       </c>
       <c r="AQ2">
-        <v>26.24641833810888</v>
+        <v>-90.53719008264463</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aplus Asset Advisor Co. Ltd (KOSE:A244920)</t>
+          <t>INCAR FINANCIAL SERVICE Co., Ltd. (KOSDAQ:A211050)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,122 +709,232 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0199</v>
-      </c>
-      <c r="E3">
-        <v>0.409</v>
-      </c>
       <c r="G3">
-        <v>0.1628721541155867</v>
+        <v>0.09709864603481626</v>
       </c>
       <c r="H3">
-        <v>0.1628721541155867</v>
+        <v>0.09709864603481626</v>
       </c>
       <c r="I3">
-        <v>0.04010507880910683</v>
+        <v>0.06963249516441006</v>
       </c>
       <c r="J3">
-        <v>0.03176744400405568</v>
+        <v>0.05485017775520569</v>
       </c>
       <c r="K3">
-        <v>15.9</v>
+        <v>14.1</v>
       </c>
       <c r="L3">
-        <v>0.06961471103327496</v>
+        <v>0.05454545454545454</v>
       </c>
       <c r="M3">
-        <v>6.6896</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03979535990481856</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.4207295597484277</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>6.6896</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03979535990481856</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.4207295597484277</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>22.8</v>
+        <v>3.31</v>
       </c>
       <c r="V3">
-        <v>0.1356335514574658</v>
-      </c>
-      <c r="W3">
-        <v>0.232796486090776</v>
+        <v>0.0604014598540146</v>
       </c>
       <c r="X3">
-        <v>0.05332407744886498</v>
-      </c>
-      <c r="Y3">
-        <v>0.179472408641911</v>
-      </c>
-      <c r="Z3">
-        <v>2.799877413423231</v>
-      </c>
-      <c r="AA3">
-        <v>0.08894494894914272</v>
+        <v>0.09074884329259292</v>
       </c>
       <c r="AB3">
-        <v>0.04798775604345278</v>
-      </c>
-      <c r="AC3">
-        <v>0.04095719290568994</v>
+        <v>0.07935345139805963</v>
       </c>
       <c r="AD3">
-        <v>41.6</v>
+        <v>18.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>41.6</v>
+        <v>18.6</v>
       </c>
       <c r="AG3">
-        <v>18.8</v>
+        <v>15.29</v>
       </c>
       <c r="AH3">
-        <v>0.1983786361468765</v>
+        <v>0.2534059945504087</v>
       </c>
       <c r="AI3">
-        <v>0.2788203753351207</v>
+        <v>0.281391830559758</v>
       </c>
       <c r="AJ3">
-        <v>0.1005885500267523</v>
+        <v>0.2181480953060351</v>
       </c>
       <c r="AK3">
-        <v>0.1487341772151899</v>
+        <v>0.2435101130753305</v>
       </c>
       <c r="AL3">
-        <v>1.08</v>
+        <v>0.771</v>
       </c>
       <c r="AM3">
-        <v>0.3490000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="AN3">
-        <v>1.69795918367347</v>
+        <v>0.7294117647058824</v>
       </c>
       <c r="AO3">
-        <v>8.481481481481481</v>
+        <v>23.34630350194552</v>
       </c>
       <c r="AP3">
-        <v>0.7673469387755102</v>
+        <v>0.5996078431372549</v>
       </c>
       <c r="AQ3">
-        <v>26.24641833810888</v>
+        <v>29.12621359223301</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aplus Asset Advisor Co. Ltd (KOSE:A244920)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0259</v>
+      </c>
+      <c r="E4">
+        <v>0.293</v>
+      </c>
+      <c r="G4">
+        <v>0.1112929623567921</v>
+      </c>
+      <c r="H4">
+        <v>0.1112929623567921</v>
+      </c>
+      <c r="I4">
+        <v>0.02133115111838516</v>
+      </c>
+      <c r="J4">
+        <v>0.01631205673758865</v>
+      </c>
+      <c r="K4">
+        <v>30.7</v>
+      </c>
+      <c r="L4">
+        <v>0.1674849972722313</v>
+      </c>
+      <c r="M4">
+        <v>2.3504</v>
+      </c>
+      <c r="N4">
+        <v>0.02714087759815243</v>
+      </c>
+      <c r="O4">
+        <v>0.07656026058631922</v>
+      </c>
+      <c r="P4">
+        <v>2.3504</v>
+      </c>
+      <c r="Q4">
+        <v>0.02714087759815243</v>
+      </c>
+      <c r="R4">
+        <v>0.07656026058631922</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>32.3</v>
+      </c>
+      <c r="V4">
+        <v>0.3729792147806005</v>
+      </c>
+      <c r="W4">
+        <v>0.3672248803827751</v>
+      </c>
+      <c r="X4">
+        <v>0.0941938925132042</v>
+      </c>
+      <c r="Y4">
+        <v>0.2730309878695709</v>
+      </c>
+      <c r="Z4">
+        <v>1.813594538438706</v>
+      </c>
+      <c r="AA4">
+        <v>0.02958345700999307</v>
+      </c>
+      <c r="AB4">
+        <v>0.07916089496940483</v>
+      </c>
+      <c r="AC4">
+        <v>-0.04957743795941176</v>
+      </c>
+      <c r="AD4">
+        <v>39</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>39</v>
+      </c>
+      <c r="AG4">
+        <v>6.700000000000003</v>
+      </c>
+      <c r="AH4">
+        <v>0.3105095541401274</v>
+      </c>
+      <c r="AI4">
+        <v>0.2315914489311164</v>
+      </c>
+      <c r="AJ4">
+        <v>0.07181136120042876</v>
+      </c>
+      <c r="AK4">
+        <v>0.04922850844966938</v>
+      </c>
+      <c r="AL4">
+        <v>1.2</v>
+      </c>
+      <c r="AM4">
+        <v>-0.8600000000000001</v>
+      </c>
+      <c r="AN4">
+        <v>2.294117647058823</v>
+      </c>
+      <c r="AO4">
+        <v>3.258333333333334</v>
+      </c>
+      <c r="AP4">
+        <v>0.3941176470588237</v>
+      </c>
+      <c r="AQ4">
+        <v>-4.546511627906977</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0259</v>
+        <v>0.08109999999999999</v>
       </c>
       <c r="E2">
-        <v>0.293</v>
+        <v>-0.0361</v>
       </c>
       <c r="G2">
-        <v>0.102987777274785</v>
+        <v>0.07529145077720208</v>
       </c>
       <c r="H2">
-        <v>0.102987777274785</v>
+        <v>0.07529145077720208</v>
       </c>
       <c r="I2">
-        <v>0.04959257582616568</v>
+        <v>0.05030764248704663</v>
       </c>
       <c r="J2">
-        <v>0.03849413871225874</v>
+        <v>0.04135280702430757</v>
       </c>
       <c r="K2">
-        <v>44.8</v>
+        <v>31.2</v>
       </c>
       <c r="L2">
-        <v>0.101403349932096</v>
+        <v>0.05051813471502591</v>
       </c>
       <c r="M2">
-        <v>2.3504</v>
+        <v>5.664300000000001</v>
       </c>
       <c r="N2">
-        <v>0.01662234794908063</v>
+        <v>0.02794425259003454</v>
       </c>
       <c r="O2">
-        <v>0.05246428571428572</v>
+        <v>0.181548076923077</v>
       </c>
       <c r="P2">
-        <v>2.3504</v>
+        <v>5.664300000000001</v>
       </c>
       <c r="Q2">
-        <v>0.01662234794908063</v>
+        <v>0.02794425259003454</v>
       </c>
       <c r="R2">
-        <v>0.05246428571428572</v>
+        <v>0.181548076923077</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>35.61</v>
+        <v>15.173</v>
       </c>
       <c r="V2">
-        <v>0.2518387553041019</v>
+        <v>0.07485446472619635</v>
+      </c>
+      <c r="W2">
+        <v>0.2602683178534572</v>
       </c>
       <c r="X2">
-        <v>0.09247136790289856</v>
+        <v>0.08457602438729689</v>
+      </c>
+      <c r="Y2">
+        <v>0.1756922934661603</v>
       </c>
       <c r="Z2">
-        <v>4.371227861877907</v>
+        <v>3.736237144585602</v>
+      </c>
+      <c r="AA2">
+        <v>0.1883688179636263</v>
       </c>
       <c r="AB2">
-        <v>0.07925717318373224</v>
+        <v>0.06947547258681705</v>
+      </c>
+      <c r="AC2">
+        <v>0.1188933453768092</v>
       </c>
       <c r="AD2">
-        <v>57.6</v>
+        <v>99.30000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>57.6</v>
+        <v>99.30000000000001</v>
       </c>
       <c r="AG2">
-        <v>21.99</v>
+        <v>84.12700000000001</v>
       </c>
       <c r="AH2">
-        <v>0.2894472361809046</v>
+        <v>0.3288079470198676</v>
       </c>
       <c r="AI2">
-        <v>0.2456289978678038</v>
+        <v>0.3218800648298217</v>
       </c>
       <c r="AJ2">
-        <v>0.1345859599730706</v>
+        <v>0.2933022344479425</v>
       </c>
       <c r="AK2">
-        <v>0.1105636281361557</v>
+        <v>0.2868027832419109</v>
       </c>
       <c r="AL2">
-        <v>1.971</v>
+        <v>6.31</v>
       </c>
       <c r="AM2">
-        <v>-0.242</v>
+        <v>0.1909999999999998</v>
       </c>
       <c r="AN2">
-        <v>1.355294117647059</v>
+        <v>1.849162011173185</v>
       </c>
       <c r="AO2">
-        <v>11.11618467782851</v>
+        <v>4.92393026941363</v>
       </c>
       <c r="AP2">
-        <v>0.5174117647058823</v>
+        <v>1.566610800744879</v>
       </c>
       <c r="AQ2">
-        <v>-90.53719008264463</v>
+        <v>162.670157068063</v>
       </c>
     </row>
     <row r="3">
@@ -710,97 +722,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.09709864603481626</v>
+        <v>0.08181818181818182</v>
       </c>
       <c r="H3">
-        <v>0.09709864603481626</v>
+        <v>0.08181818181818182</v>
       </c>
       <c r="I3">
-        <v>0.06963249516441006</v>
+        <v>0.07326203208556149</v>
       </c>
       <c r="J3">
-        <v>0.05485017775520569</v>
+        <v>0.05813798168506575</v>
       </c>
       <c r="K3">
-        <v>14.1</v>
+        <v>18.5</v>
       </c>
       <c r="L3">
-        <v>0.05454545454545454</v>
+        <v>0.04946524064171123</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.2969</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01814296998420221</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1241567567567568</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.2969</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01814296998420221</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1241567567567568</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>3.31</v>
+        <v>0.573</v>
       </c>
       <c r="V3">
-        <v>0.0604014598540146</v>
+        <v>0.0045260663507109</v>
+      </c>
+      <c r="W3">
+        <v>0.3894736842105263</v>
       </c>
       <c r="X3">
-        <v>0.09074884329259292</v>
+        <v>0.0826628783733182</v>
+      </c>
+      <c r="Y3">
+        <v>0.3068108058372081</v>
+      </c>
+      <c r="Z3">
+        <v>5.956362478101609</v>
+      </c>
+      <c r="AA3">
+        <v>0.3462908926614842</v>
       </c>
       <c r="AB3">
-        <v>0.07935345139805963</v>
+        <v>0.07044718230044274</v>
+      </c>
+      <c r="AC3">
+        <v>0.2758437103610415</v>
       </c>
       <c r="AD3">
-        <v>18.6</v>
+        <v>54.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.6</v>
+        <v>54.7</v>
       </c>
       <c r="AG3">
-        <v>15.29</v>
+        <v>54.127</v>
       </c>
       <c r="AH3">
-        <v>0.2534059945504087</v>
+        <v>0.3017098731384446</v>
       </c>
       <c r="AI3">
-        <v>0.281391830559758</v>
+        <v>0.4502057613168725</v>
       </c>
       <c r="AJ3">
-        <v>0.2181480953060351</v>
+        <v>0.299495924792643</v>
       </c>
       <c r="AK3">
-        <v>0.2435101130753305</v>
+        <v>0.4476006185549961</v>
       </c>
       <c r="AL3">
-        <v>0.771</v>
+        <v>5.02</v>
       </c>
       <c r="AM3">
-        <v>0.618</v>
+        <v>4.100999999999999</v>
       </c>
       <c r="AN3">
-        <v>0.7294117647058824</v>
+        <v>1.515235457063712</v>
       </c>
       <c r="AO3">
-        <v>23.34630350194552</v>
+        <v>5.458167330677291</v>
       </c>
       <c r="AP3">
-        <v>0.5996078431372549</v>
+        <v>1.499362880886427</v>
       </c>
       <c r="AQ3">
-        <v>29.12621359223301</v>
+        <v>6.681297244574496</v>
       </c>
     </row>
     <row r="4">
@@ -820,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0259</v>
+        <v>0.08109999999999999</v>
       </c>
       <c r="E4">
-        <v>0.293</v>
+        <v>-0.0361</v>
       </c>
       <c r="G4">
-        <v>0.1112929623567921</v>
+        <v>0.06527093596059114</v>
       </c>
       <c r="H4">
-        <v>0.1112929623567921</v>
+        <v>0.06527093596059114</v>
       </c>
       <c r="I4">
-        <v>0.02133115111838516</v>
+        <v>0.01506568144499179</v>
       </c>
       <c r="J4">
-        <v>0.01631205673758865</v>
+        <v>0.01281237952452345</v>
       </c>
       <c r="K4">
-        <v>30.7</v>
+        <v>12.7</v>
       </c>
       <c r="L4">
-        <v>0.1674849972722313</v>
+        <v>0.05213464696223317</v>
       </c>
       <c r="M4">
-        <v>2.3504</v>
+        <v>3.3674</v>
       </c>
       <c r="N4">
-        <v>0.02714087759815243</v>
+        <v>0.04424967148488831</v>
       </c>
       <c r="O4">
-        <v>0.07656026058631922</v>
+        <v>0.2651496062992126</v>
       </c>
       <c r="P4">
-        <v>2.3504</v>
+        <v>3.3674</v>
       </c>
       <c r="Q4">
-        <v>0.02714087759815243</v>
+        <v>0.04424967148488831</v>
       </c>
       <c r="R4">
-        <v>0.07656026058631922</v>
+        <v>0.2651496062992126</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -868,73 +898,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>32.3</v>
+        <v>14.6</v>
       </c>
       <c r="V4">
-        <v>0.3729792147806005</v>
+        <v>0.1918528252299606</v>
       </c>
       <c r="W4">
-        <v>0.3672248803827751</v>
+        <v>0.131062951496388</v>
       </c>
       <c r="X4">
-        <v>0.0941938925132042</v>
+        <v>0.08648917040127557</v>
       </c>
       <c r="Y4">
-        <v>0.2730309878695709</v>
+        <v>0.04457378109511245</v>
       </c>
       <c r="Z4">
-        <v>1.813594538438706</v>
+        <v>2.376353526485221</v>
       </c>
       <c r="AA4">
-        <v>0.02958345700999307</v>
+        <v>0.03044674326576834</v>
       </c>
       <c r="AB4">
-        <v>0.07916089496940483</v>
+        <v>0.06850376287319138</v>
       </c>
       <c r="AC4">
-        <v>-0.04957743795941176</v>
+        <v>-0.03805701960742303</v>
       </c>
       <c r="AD4">
-        <v>39</v>
+        <v>44.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>39</v>
+        <v>44.6</v>
       </c>
       <c r="AG4">
-        <v>6.700000000000003</v>
+        <v>30</v>
       </c>
       <c r="AH4">
-        <v>0.3105095541401274</v>
+        <v>0.3695111847555924</v>
       </c>
       <c r="AI4">
-        <v>0.2315914489311164</v>
+        <v>0.2385026737967915</v>
       </c>
       <c r="AJ4">
-        <v>0.07181136120042876</v>
+        <v>0.2827521206409048</v>
       </c>
       <c r="AK4">
-        <v>0.04922850844966938</v>
+        <v>0.1740139211136891</v>
       </c>
       <c r="AL4">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AM4">
-        <v>-0.8600000000000001</v>
+        <v>-3.91</v>
       </c>
       <c r="AN4">
-        <v>2.294117647058823</v>
+        <v>2.534090909090909</v>
       </c>
       <c r="AO4">
-        <v>3.258333333333334</v>
+        <v>2.844961240310077</v>
       </c>
       <c r="AP4">
-        <v>0.3941176470588237</v>
+        <v>1.704545454545454</v>
       </c>
       <c r="AQ4">
-        <v>-4.546511627906977</v>
+        <v>-0.938618925831202</v>
       </c>
     </row>
   </sheetData>
